--- a/ig/main/ValueSet-JDV-J150-MethodBP-ENS.xlsx
+++ b/ig/main/ValueSet-JDV-J150-MethodBP-ENS.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.0</t>
+    <t>20231215120000</t>
   </si>
   <si>
     <t>Name</t>

--- a/ig/main/ValueSet-JDV-J150-MethodBP-ENS.xlsx
+++ b/ig/main/ValueSet-JDV-J150-MethodBP-ENS.xlsx
@@ -81,7 +81,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France</t>
   </si>
   <si>
     <t>Description</t>

--- a/ig/main/ValueSet-JDV-J150-MethodBP-ENS.xlsx
+++ b/ig/main/ValueSet-JDV-J150-MethodBP-ENS.xlsx
@@ -7,7 +7,7 @@
   </bookViews>
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
-    <sheet name="Include from emdn" r:id="rId4" sheetId="2"/>
+    <sheet name="Include from EMDN" r:id="rId4" sheetId="2"/>
   </sheets>
 </workbook>
 </file>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20231215120000</t>
+    <t>20240726120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-15T12:00:00+01:00</t>
+    <t>2024-07-26T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -135,7 +135,7 @@
     <t>System URI</t>
   </si>
   <si>
-    <t>https://webgate.ec.europa.eu/dyna2/emdn</t>
+    <t>https://smt.esante.gouv.fr/terminologie-emdn</t>
   </si>
 </sst>
 </file>

--- a/ig/main/ValueSet-JDV-J150-MethodBP-ENS.xlsx
+++ b/ig/main/ValueSet-JDV-J150-MethodBP-ENS.xlsx
@@ -7,7 +7,7 @@
   </bookViews>
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
-    <sheet name="Include from EMDN" r:id="rId4" sheetId="2"/>
+    <sheet name="Include #0" r:id="rId4" sheetId="2"/>
   </sheets>
 </workbook>
 </file>
